--- a/output/yearly_population_iteration_84_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_84_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4851</v>
+        <v>4949</v>
       </c>
       <c r="C2" t="n">
-        <v>7197</v>
+        <v>10438</v>
       </c>
       <c r="D2" t="n">
-        <v>18946</v>
+        <v>28508</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3431</v>
+        <v>3482</v>
       </c>
       <c r="C3" t="n">
-        <v>3884</v>
+        <v>4473</v>
       </c>
       <c r="D3" t="n">
-        <v>15802</v>
+        <v>18014</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2774</v>
+        <v>2591</v>
       </c>
       <c r="C4" t="n">
-        <v>3795</v>
+        <v>5227</v>
       </c>
       <c r="D4" t="n">
-        <v>8892</v>
+        <v>8137</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1845</v>
+        <v>1656</v>
       </c>
       <c r="C5" t="n">
-        <v>3457</v>
+        <v>4057</v>
       </c>
       <c r="D5" t="n">
-        <v>3294</v>
+        <v>2851</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1054</v>
+        <v>939</v>
       </c>
       <c r="C6" t="n">
-        <v>2498</v>
+        <v>2611</v>
       </c>
       <c r="D6" t="n">
-        <v>1280</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>511</v>
+        <v>434</v>
       </c>
       <c r="C7" t="n">
-        <v>1477</v>
+        <v>1762</v>
       </c>
       <c r="D7" t="n">
-        <v>667</v>
+        <v>650</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="C8" t="n">
-        <v>716</v>
+        <v>956</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>335</v>
+        <v>413</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
         <v>243</v>
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -948,7 +948,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>76</v>
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1052,7 +1052,7 @@
         <v>98</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8088</v>
+        <v>6993</v>
       </c>
       <c r="C2" t="n">
-        <v>5739</v>
+        <v>5811</v>
       </c>
       <c r="D2" t="n">
-        <v>20488</v>
+        <v>24886</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3334</v>
+        <v>3383</v>
       </c>
       <c r="C3" t="n">
-        <v>4763</v>
+        <v>6322</v>
       </c>
       <c r="D3" t="n">
-        <v>15167</v>
+        <v>18230</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2651</v>
+        <v>2570</v>
       </c>
       <c r="C4" t="n">
-        <v>3723</v>
+        <v>4756</v>
       </c>
       <c r="D4" t="n">
-        <v>9664</v>
+        <v>9501</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1991</v>
+        <v>1816</v>
       </c>
       <c r="C5" t="n">
-        <v>3547</v>
+        <v>4472</v>
       </c>
       <c r="D5" t="n">
-        <v>4107</v>
+        <v>3548</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1275</v>
+        <v>1134</v>
       </c>
       <c r="C6" t="n">
-        <v>2890</v>
+        <v>3237</v>
       </c>
       <c r="D6" t="n">
-        <v>1559</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>677</v>
+        <v>586</v>
       </c>
       <c r="C7" t="n">
-        <v>1946</v>
+        <v>2118</v>
       </c>
       <c r="D7" t="n">
-        <v>756</v>
+        <v>710</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>287</v>
+        <v>241</v>
       </c>
       <c r="C8" t="n">
-        <v>1044</v>
+        <v>1303</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>499</v>
+        <v>632</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>261</v>
+        <v>299</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1251,7 +1251,7 @@
         <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8185</v>
+        <v>8233</v>
       </c>
       <c r="C2" t="n">
-        <v>7910</v>
+        <v>13330</v>
       </c>
       <c r="D2" t="n">
-        <v>27367</v>
+        <v>22989</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4256</v>
+        <v>3912</v>
       </c>
       <c r="C3" t="n">
-        <v>4581</v>
+        <v>5415</v>
       </c>
       <c r="D3" t="n">
-        <v>14853</v>
+        <v>17886</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2508</v>
+        <v>2474</v>
       </c>
       <c r="C4" t="n">
-        <v>4079</v>
+        <v>5348</v>
       </c>
       <c r="D4" t="n">
-        <v>10122</v>
+        <v>10552</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2017</v>
+        <v>1884</v>
       </c>
       <c r="C5" t="n">
-        <v>3550</v>
+        <v>4456</v>
       </c>
       <c r="D5" t="n">
-        <v>4835</v>
+        <v>4263</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1434</v>
+        <v>1295</v>
       </c>
       <c r="C6" t="n">
-        <v>3112</v>
+        <v>3685</v>
       </c>
       <c r="D6" t="n">
-        <v>1890</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>836</v>
+        <v>719</v>
       </c>
       <c r="C7" t="n">
-        <v>2323</v>
+        <v>2577</v>
       </c>
       <c r="D7" t="n">
-        <v>866</v>
+        <v>790</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>390</v>
+        <v>330</v>
       </c>
       <c r="C8" t="n">
-        <v>1414</v>
+        <v>1609</v>
       </c>
       <c r="D8" t="n">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="C9" t="n">
-        <v>707</v>
+        <v>882</v>
       </c>
       <c r="D9" t="n">
-        <v>339</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>351</v>
+        <v>422</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="D11" t="n">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1576,7 +1576,7 @@
         <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7428</v>
+        <v>7427</v>
       </c>
       <c r="C2" t="n">
-        <v>5252</v>
+        <v>9064</v>
       </c>
       <c r="D2" t="n">
-        <v>22245</v>
+        <v>19078</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4892</v>
+        <v>4607</v>
       </c>
       <c r="C3" t="n">
-        <v>7079</v>
+        <v>8954</v>
       </c>
       <c r="D3" t="n">
-        <v>16919</v>
+        <v>19725</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1863</v>
+        <v>1740</v>
       </c>
       <c r="C4" t="n">
-        <v>5718</v>
+        <v>7255</v>
       </c>
       <c r="D4" t="n">
-        <v>10000</v>
+        <v>9834</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1325</v>
+        <v>1196</v>
       </c>
       <c r="C5" t="n">
-        <v>3049</v>
+        <v>3611</v>
       </c>
       <c r="D5" t="n">
-        <v>3198</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>772</v>
+        <v>664</v>
       </c>
       <c r="C6" t="n">
-        <v>2276</v>
+        <v>2525</v>
       </c>
       <c r="D6" t="n">
-        <v>848</v>
+        <v>774</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>360</v>
+        <v>304</v>
       </c>
       <c r="C7" t="n">
-        <v>1385</v>
+        <v>1576</v>
       </c>
       <c r="D7" t="n">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="C8" t="n">
-        <v>692</v>
+        <v>864</v>
       </c>
       <c r="D8" t="n">
-        <v>332</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>343</v>
+        <v>413</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1873,7 +1873,7 @@
         <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4544</v>
+        <v>4435</v>
       </c>
       <c r="C2" t="n">
-        <v>2835</v>
+        <v>4516</v>
       </c>
       <c r="D2" t="n">
-        <v>15252</v>
+        <v>13543</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5163</v>
+        <v>4967</v>
       </c>
       <c r="C3" t="n">
-        <v>5624</v>
+        <v>8154</v>
       </c>
       <c r="D3" t="n">
-        <v>16846</v>
+        <v>18500</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2675</v>
+        <v>2446</v>
       </c>
       <c r="C4" t="n">
-        <v>6471</v>
+        <v>8181</v>
       </c>
       <c r="D4" t="n">
-        <v>10950</v>
+        <v>11243</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1453</v>
+        <v>1321</v>
       </c>
       <c r="C5" t="n">
-        <v>4259</v>
+        <v>5213</v>
       </c>
       <c r="D5" t="n">
-        <v>4011</v>
+        <v>3646</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>930</v>
+        <v>799</v>
       </c>
       <c r="C6" t="n">
-        <v>2666</v>
+        <v>3029</v>
       </c>
       <c r="D6" t="n">
-        <v>1088</v>
+        <v>981</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>342</v>
+        <v>287</v>
       </c>
       <c r="C7" t="n">
-        <v>1759</v>
+        <v>1974</v>
       </c>
       <c r="D7" t="n">
-        <v>524</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>908</v>
+        <v>1103</v>
       </c>
       <c r="D8" t="n">
-        <v>346</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>403</v>
+        <v>470</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
+        <v>166</v>
+      </c>
+      <c r="D11" t="n">
         <v>167</v>
-      </c>
-      <c r="D11" t="n">
-        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6359</v>
+        <v>5043</v>
       </c>
       <c r="C2" t="n">
-        <v>8732</v>
+        <v>10467</v>
       </c>
       <c r="D2" t="n">
-        <v>16731</v>
+        <v>14508</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4106</v>
+        <v>3980</v>
       </c>
       <c r="C3" t="n">
-        <v>3762</v>
+        <v>5714</v>
       </c>
       <c r="D3" t="n">
-        <v>15457</v>
+        <v>16690</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3258</v>
+        <v>3048</v>
       </c>
       <c r="C4" t="n">
-        <v>5905</v>
+        <v>7997</v>
       </c>
       <c r="D4" t="n">
-        <v>11635</v>
+        <v>12085</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1757</v>
+        <v>1593</v>
       </c>
       <c r="C5" t="n">
-        <v>5294</v>
+        <v>6500</v>
       </c>
       <c r="D5" t="n">
-        <v>5021</v>
+        <v>4702</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1063</v>
+        <v>934</v>
       </c>
       <c r="C6" t="n">
-        <v>3373</v>
+        <v>4014</v>
       </c>
       <c r="D6" t="n">
-        <v>1522</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>513</v>
+        <v>431</v>
       </c>
       <c r="C7" t="n">
-        <v>2184</v>
+        <v>2447</v>
       </c>
       <c r="D7" t="n">
-        <v>601</v>
+        <v>577</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="C8" t="n">
-        <v>1275</v>
+        <v>1463</v>
       </c>
       <c r="D8" t="n">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>604</v>
+        <v>710</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>293</v>
+        <v>320</v>
       </c>
       <c r="D10" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -2509,7 +2509,7 @@
         <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3657</v>
+        <v>2966</v>
       </c>
       <c r="C2" t="n">
-        <v>3948</v>
+        <v>4880</v>
       </c>
       <c r="D2" t="n">
-        <v>11575</v>
+        <v>10155</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4550</v>
+        <v>4086</v>
       </c>
       <c r="C3" t="n">
-        <v>5385</v>
+        <v>7137</v>
       </c>
       <c r="D3" t="n">
-        <v>15228</v>
+        <v>16089</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3609</v>
+        <v>3366</v>
       </c>
       <c r="C4" t="n">
-        <v>5608</v>
+        <v>7853</v>
       </c>
       <c r="D4" t="n">
-        <v>12206</v>
+        <v>12740</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1845</v>
+        <v>1660</v>
       </c>
       <c r="C5" t="n">
-        <v>6168</v>
+        <v>7751</v>
       </c>
       <c r="D5" t="n">
-        <v>5416</v>
+        <v>4962</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>925</v>
+        <v>777</v>
       </c>
       <c r="C6" t="n">
-        <v>4221</v>
+        <v>4878</v>
       </c>
       <c r="D6" t="n">
-        <v>1483</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="C7" t="n">
-        <v>2335</v>
+        <v>2619</v>
       </c>
       <c r="D7" t="n">
-        <v>601</v>
+        <v>577</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>1004</v>
+        <v>1140</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>287</v>
+        <v>313</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2806,7 +2806,7 @@
         <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4320</v>
+        <v>3165</v>
       </c>
       <c r="C2" t="n">
-        <v>8180</v>
+        <v>6312</v>
       </c>
       <c r="D2" t="n">
-        <v>18634</v>
+        <v>19015</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3545</v>
+        <v>3096</v>
       </c>
       <c r="C3" t="n">
-        <v>4175</v>
+        <v>5446</v>
       </c>
       <c r="D3" t="n">
-        <v>13800</v>
+        <v>14355</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3526</v>
+        <v>3193</v>
       </c>
       <c r="C4" t="n">
-        <v>5382</v>
+        <v>7352</v>
       </c>
       <c r="D4" t="n">
-        <v>12328</v>
+        <v>12867</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2279</v>
+        <v>2075</v>
       </c>
       <c r="C5" t="n">
-        <v>5835</v>
+        <v>7710</v>
       </c>
       <c r="D5" t="n">
-        <v>6294</v>
+        <v>5931</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1177</v>
+        <v>1014</v>
       </c>
       <c r="C6" t="n">
-        <v>5123</v>
+        <v>6094</v>
       </c>
       <c r="D6" t="n">
-        <v>2044</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>353</v>
+        <v>291</v>
       </c>
       <c r="C7" t="n">
-        <v>3133</v>
+        <v>3576</v>
       </c>
       <c r="D7" t="n">
-        <v>707</v>
+        <v>671</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="C8" t="n">
-        <v>1541</v>
+        <v>1698</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>531</v>
+        <v>589</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
         <v>136</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2964</v>
+        <v>2172</v>
       </c>
       <c r="C2" t="n">
-        <v>4148</v>
+        <v>4139</v>
       </c>
       <c r="D2" t="n">
-        <v>14320</v>
+        <v>13745</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3332</v>
+        <v>2732</v>
       </c>
       <c r="C3" t="n">
-        <v>5320</v>
+        <v>5254</v>
       </c>
       <c r="D3" t="n">
-        <v>13778</v>
+        <v>14133</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3249</v>
+        <v>2913</v>
       </c>
       <c r="C4" t="n">
-        <v>4915</v>
+        <v>6642</v>
       </c>
       <c r="D4" t="n">
-        <v>12269</v>
+        <v>12922</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2531</v>
+        <v>2266</v>
       </c>
       <c r="C5" t="n">
-        <v>5712</v>
+        <v>7644</v>
       </c>
       <c r="D5" t="n">
-        <v>6918</v>
+        <v>6540</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1383</v>
+        <v>1207</v>
       </c>
       <c r="C6" t="n">
-        <v>5569</v>
+        <v>6847</v>
       </c>
       <c r="D6" t="n">
-        <v>2426</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>342</v>
+        <v>263</v>
       </c>
       <c r="C7" t="n">
-        <v>3873</v>
+        <v>4436</v>
       </c>
       <c r="D7" t="n">
-        <v>807</v>
+        <v>750</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1987</v>
+        <v>2187</v>
       </c>
       <c r="D8" t="n">
-        <v>434</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>638</v>
+        <v>664</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
         <v>137</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4366</v>
+        <v>4143</v>
       </c>
       <c r="C2" t="n">
-        <v>11014</v>
+        <v>11339</v>
       </c>
       <c r="D2" t="n">
-        <v>12264</v>
+        <v>18597</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2689</v>
+        <v>2138</v>
       </c>
       <c r="C3" t="n">
-        <v>4284</v>
+        <v>4281</v>
       </c>
       <c r="D3" t="n">
-        <v>12943</v>
+        <v>13181</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2849</v>
+        <v>2477</v>
       </c>
       <c r="C4" t="n">
-        <v>4991</v>
+        <v>5917</v>
       </c>
       <c r="D4" t="n">
-        <v>12127</v>
+        <v>12703</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2535</v>
+        <v>2263</v>
       </c>
       <c r="C5" t="n">
-        <v>5256</v>
+        <v>7080</v>
       </c>
       <c r="D5" t="n">
-        <v>7478</v>
+        <v>7198</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1666</v>
+        <v>1452</v>
       </c>
       <c r="C6" t="n">
-        <v>5577</v>
+        <v>7095</v>
       </c>
       <c r="D6" t="n">
-        <v>2998</v>
+        <v>2695</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>614</v>
+        <v>494</v>
       </c>
       <c r="C7" t="n">
-        <v>4574</v>
+        <v>5375</v>
       </c>
       <c r="D7" t="n">
-        <v>1005</v>
+        <v>910</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>2670</v>
+        <v>2957</v>
       </c>
       <c r="D8" t="n">
-        <v>473</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>1106</v>
+        <v>1162</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D10" t="n">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
         <v>64</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6173</v>
+        <v>4580</v>
       </c>
       <c r="C2" t="n">
-        <v>5665</v>
+        <v>9258</v>
       </c>
       <c r="D2" t="n">
-        <v>7693</v>
+        <v>9780</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3090</v>
+        <v>2993</v>
       </c>
       <c r="C2" t="n">
-        <v>6167</v>
+        <v>6532</v>
       </c>
       <c r="D2" t="n">
-        <v>9026</v>
+        <v>13836</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3584</v>
+        <v>2954</v>
       </c>
       <c r="C3" t="n">
-        <v>6262</v>
+        <v>6238</v>
       </c>
       <c r="D3" t="n">
-        <v>13908</v>
+        <v>14548</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3802</v>
+        <v>3357</v>
       </c>
       <c r="C4" t="n">
-        <v>6849</v>
+        <v>8334</v>
       </c>
       <c r="D4" t="n">
-        <v>12666</v>
+        <v>13068</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1633</v>
+        <v>1383</v>
       </c>
       <c r="C5" t="n">
-        <v>7744</v>
+        <v>10185</v>
       </c>
       <c r="D5" t="n">
-        <v>6924</v>
+        <v>6503</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>567</v>
+        <v>456</v>
       </c>
       <c r="C6" t="n">
-        <v>5684</v>
+        <v>6588</v>
       </c>
       <c r="D6" t="n">
-        <v>2316</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>2616</v>
+        <v>2897</v>
       </c>
       <c r="D7" t="n">
-        <v>601</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>1083</v>
+        <v>1138</v>
       </c>
       <c r="D8" t="n">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D9" t="n">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
         <v>62</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6876</v>
+        <v>6201</v>
       </c>
       <c r="C2" t="n">
-        <v>4518</v>
+        <v>5308</v>
       </c>
       <c r="D2" t="n">
-        <v>21309</v>
+        <v>17247</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2622</v>
+        <v>1947</v>
       </c>
       <c r="C3" t="n">
-        <v>2855</v>
+        <v>4666</v>
       </c>
       <c r="D3" t="n">
-        <v>1931</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4891</v>
+        <v>4704</v>
       </c>
       <c r="C2" t="n">
-        <v>4835</v>
+        <v>4862</v>
       </c>
       <c r="D2" t="n">
-        <v>36926</v>
+        <v>17870</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3900</v>
+        <v>3342</v>
       </c>
       <c r="C3" t="n">
-        <v>3273</v>
+        <v>4337</v>
       </c>
       <c r="D3" t="n">
-        <v>5044</v>
+        <v>4628</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1172</v>
+        <v>880</v>
       </c>
       <c r="C4" t="n">
-        <v>1715</v>
+        <v>2778</v>
       </c>
       <c r="D4" t="n">
-        <v>1570</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5162</v>
+        <v>5200</v>
       </c>
       <c r="C2" t="n">
-        <v>6644</v>
+        <v>4403</v>
       </c>
       <c r="D2" t="n">
-        <v>26327</v>
+        <v>25383</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3611</v>
+        <v>3296</v>
       </c>
       <c r="C3" t="n">
-        <v>3570</v>
+        <v>4001</v>
       </c>
       <c r="D3" t="n">
-        <v>9781</v>
+        <v>6413</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2157</v>
+        <v>1792</v>
       </c>
       <c r="C4" t="n">
-        <v>2561</v>
+        <v>3603</v>
       </c>
       <c r="D4" t="n">
-        <v>2189</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>531</v>
+        <v>414</v>
       </c>
       <c r="C5" t="n">
-        <v>1033</v>
+        <v>1614</v>
       </c>
       <c r="D5" t="n">
-        <v>1208</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>631</v>
+        <v>620</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5319,7 +5319,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5525</v>
+        <v>4853</v>
       </c>
       <c r="C2" t="n">
-        <v>5199</v>
+        <v>5748</v>
       </c>
       <c r="D2" t="n">
-        <v>32286</v>
+        <v>29719</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3571</v>
+        <v>3443</v>
       </c>
       <c r="C3" t="n">
-        <v>4484</v>
+        <v>3662</v>
       </c>
       <c r="D3" t="n">
-        <v>11607</v>
+        <v>8844</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2456</v>
+        <v>2159</v>
       </c>
       <c r="C4" t="n">
-        <v>3050</v>
+        <v>3742</v>
       </c>
       <c r="D4" t="n">
-        <v>3507</v>
+        <v>2873</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1101</v>
+        <v>901</v>
       </c>
       <c r="C5" t="n">
-        <v>1793</v>
+        <v>2596</v>
       </c>
       <c r="D5" t="n">
-        <v>1329</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>295</v>
+        <v>247</v>
       </c>
       <c r="C6" t="n">
-        <v>672</v>
+        <v>965</v>
       </c>
       <c r="D6" t="n">
-        <v>948</v>
+        <v>951</v>
       </c>
     </row>
     <row r="7">
@@ -5521,7 +5521,7 @@
         <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>655</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9">
@@ -5560,7 +5560,7 @@
         <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6487</v>
+        <v>5583</v>
       </c>
       <c r="C2" t="n">
-        <v>5947</v>
+        <v>10274</v>
       </c>
       <c r="D2" t="n">
-        <v>32278</v>
+        <v>43166</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3285</v>
+        <v>3004</v>
       </c>
       <c r="C3" t="n">
-        <v>3972</v>
+        <v>3873</v>
       </c>
       <c r="D3" t="n">
-        <v>13108</v>
+        <v>10719</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1858</v>
+        <v>1726</v>
       </c>
       <c r="C4" t="n">
-        <v>3146</v>
+        <v>3028</v>
       </c>
       <c r="D4" t="n">
-        <v>4257</v>
+        <v>3381</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>933</v>
+        <v>799</v>
       </c>
       <c r="C5" t="n">
-        <v>1773</v>
+        <v>2309</v>
       </c>
       <c r="D5" t="n">
-        <v>1338</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>327</v>
+        <v>269</v>
       </c>
       <c r="C6" t="n">
-        <v>833</v>
+        <v>1204</v>
       </c>
       <c r="D6" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
-        <v>323</v>
+        <v>414</v>
       </c>
       <c r="D7" t="n">
-        <v>516</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5857,7 +5857,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
         <v>269</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5329</v>
+        <v>5577</v>
       </c>
       <c r="C2" t="n">
-        <v>4508</v>
+        <v>6411</v>
       </c>
       <c r="D2" t="n">
-        <v>28290</v>
+        <v>31831</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4065</v>
+        <v>3570</v>
       </c>
       <c r="C3" t="n">
-        <v>4455</v>
+        <v>6553</v>
       </c>
       <c r="D3" t="n">
-        <v>15363</v>
+        <v>15381</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2259</v>
+        <v>2077</v>
       </c>
       <c r="C4" t="n">
-        <v>3549</v>
+        <v>3476</v>
       </c>
       <c r="D4" t="n">
-        <v>5871</v>
+        <v>4725</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1238</v>
+        <v>1126</v>
       </c>
       <c r="C5" t="n">
-        <v>2553</v>
+        <v>2682</v>
       </c>
       <c r="D5" t="n">
-        <v>1885</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>588</v>
+        <v>491</v>
       </c>
       <c r="C6" t="n">
-        <v>1364</v>
+        <v>1803</v>
       </c>
       <c r="D6" t="n">
-        <v>861</v>
+        <v>855</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="C7" t="n">
-        <v>612</v>
+        <v>862</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>277</v>
+        <v>327</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10">
@@ -6182,7 +6182,7 @@
         <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
         <v>240</v>
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
         <v>120</v>
@@ -6238,7 +6238,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4506</v>
+        <v>4808</v>
       </c>
       <c r="C2" t="n">
-        <v>5017</v>
+        <v>4626</v>
       </c>
       <c r="D2" t="n">
-        <v>20446</v>
+        <v>32690</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3855</v>
+        <v>3737</v>
       </c>
       <c r="C3" t="n">
-        <v>3881</v>
+        <v>5605</v>
       </c>
       <c r="D3" t="n">
-        <v>16325</v>
+        <v>16905</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2697</v>
+        <v>2428</v>
       </c>
       <c r="C4" t="n">
-        <v>3954</v>
+        <v>5146</v>
       </c>
       <c r="D4" t="n">
-        <v>7514</v>
+        <v>6627</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1541</v>
+        <v>1393</v>
       </c>
       <c r="C5" t="n">
-        <v>3054</v>
+        <v>3060</v>
       </c>
       <c r="D5" t="n">
-        <v>2536</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>825</v>
+        <v>732</v>
       </c>
       <c r="C6" t="n">
-        <v>1987</v>
+        <v>2228</v>
       </c>
       <c r="D6" t="n">
-        <v>1035</v>
+        <v>987</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>345</v>
+        <v>284</v>
       </c>
       <c r="C7" t="n">
-        <v>1009</v>
+        <v>1359</v>
       </c>
       <c r="D7" t="n">
-        <v>601</v>
+        <v>591</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>447</v>
+        <v>599</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>240</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>241</v>
@@ -6524,7 +6524,7 @@
         <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -6650,7 +6650,7 @@
         <v>91</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_84_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_84_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4949</v>
+        <v>5670</v>
       </c>
       <c r="C2" t="n">
-        <v>10438</v>
+        <v>6361</v>
       </c>
       <c r="D2" t="n">
-        <v>28508</v>
+        <v>32534</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3482</v>
+        <v>2892</v>
       </c>
       <c r="C3" t="n">
-        <v>4473</v>
+        <v>3930</v>
       </c>
       <c r="D3" t="n">
-        <v>18014</v>
+        <v>16811</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2591</v>
+        <v>2353</v>
       </c>
       <c r="C4" t="n">
-        <v>5227</v>
+        <v>4964</v>
       </c>
       <c r="D4" t="n">
-        <v>8137</v>
+        <v>6923</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1656</v>
+        <v>1612</v>
       </c>
       <c r="C5" t="n">
-        <v>4057</v>
+        <v>3925</v>
       </c>
       <c r="D5" t="n">
-        <v>2851</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>939</v>
+        <v>988</v>
       </c>
       <c r="C6" t="n">
-        <v>2611</v>
+        <v>2745</v>
       </c>
       <c r="D6" t="n">
-        <v>1152</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>434</v>
+        <v>480</v>
       </c>
       <c r="C7" t="n">
-        <v>1762</v>
+        <v>1908</v>
       </c>
       <c r="D7" t="n">
-        <v>650</v>
+        <v>665</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="C8" t="n">
-        <v>956</v>
+        <v>1009</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C9" t="n">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
         <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6993</v>
+        <v>6113</v>
       </c>
       <c r="C2" t="n">
-        <v>5811</v>
+        <v>10466</v>
       </c>
       <c r="D2" t="n">
-        <v>24886</v>
+        <v>32871</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3383</v>
+        <v>3334</v>
       </c>
       <c r="C3" t="n">
-        <v>6322</v>
+        <v>4430</v>
       </c>
       <c r="D3" t="n">
-        <v>18230</v>
+        <v>17819</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2570</v>
+        <v>2237</v>
       </c>
       <c r="C4" t="n">
-        <v>4756</v>
+        <v>4316</v>
       </c>
       <c r="D4" t="n">
-        <v>9501</v>
+        <v>8259</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1816</v>
+        <v>1710</v>
       </c>
       <c r="C5" t="n">
-        <v>4472</v>
+        <v>4332</v>
       </c>
       <c r="D5" t="n">
-        <v>3548</v>
+        <v>3295</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1134</v>
+        <v>1146</v>
       </c>
       <c r="C6" t="n">
-        <v>3237</v>
+        <v>3223</v>
       </c>
       <c r="D6" t="n">
-        <v>1397</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>586</v>
+        <v>626</v>
       </c>
       <c r="C7" t="n">
-        <v>2118</v>
+        <v>2284</v>
       </c>
       <c r="D7" t="n">
-        <v>710</v>
+        <v>728</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>241</v>
+        <v>275</v>
       </c>
       <c r="C8" t="n">
-        <v>1303</v>
+        <v>1386</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C9" t="n">
-        <v>632</v>
+        <v>670</v>
       </c>
       <c r="D9" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
         <v>125</v>
@@ -1262,7 +1262,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
         <v>102</v>
@@ -1276,7 +1276,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8233</v>
+        <v>6225</v>
       </c>
       <c r="C2" t="n">
-        <v>13330</v>
+        <v>9810</v>
       </c>
       <c r="D2" t="n">
-        <v>22989</v>
+        <v>42018</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3912</v>
+        <v>3619</v>
       </c>
       <c r="C3" t="n">
-        <v>5415</v>
+        <v>6148</v>
       </c>
       <c r="D3" t="n">
-        <v>17886</v>
+        <v>18576</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2474</v>
+        <v>2280</v>
       </c>
       <c r="C4" t="n">
-        <v>5348</v>
+        <v>4235</v>
       </c>
       <c r="D4" t="n">
-        <v>10552</v>
+        <v>9476</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1884</v>
+        <v>1716</v>
       </c>
       <c r="C5" t="n">
-        <v>4456</v>
+        <v>4234</v>
       </c>
       <c r="D5" t="n">
-        <v>4263</v>
+        <v>3878</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1295</v>
+        <v>1257</v>
       </c>
       <c r="C6" t="n">
-        <v>3685</v>
+        <v>3620</v>
       </c>
       <c r="D6" t="n">
-        <v>1688</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>719</v>
+        <v>758</v>
       </c>
       <c r="C7" t="n">
-        <v>2577</v>
+        <v>2669</v>
       </c>
       <c r="D7" t="n">
-        <v>790</v>
+        <v>805</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>330</v>
+        <v>363</v>
       </c>
       <c r="C8" t="n">
-        <v>1609</v>
+        <v>1723</v>
       </c>
       <c r="D8" t="n">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="C9" t="n">
-        <v>882</v>
+        <v>936</v>
       </c>
       <c r="D9" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
@@ -1559,7 +1559,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
         <v>126</v>
@@ -1570,7 +1570,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>89</v>
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7427</v>
+        <v>5758</v>
       </c>
       <c r="C2" t="n">
-        <v>9064</v>
+        <v>6670</v>
       </c>
       <c r="D2" t="n">
-        <v>19078</v>
+        <v>34327</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4607</v>
+        <v>4255</v>
       </c>
       <c r="C3" t="n">
-        <v>8954</v>
+        <v>8786</v>
       </c>
       <c r="D3" t="n">
-        <v>19725</v>
+        <v>19939</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1740</v>
+        <v>1585</v>
       </c>
       <c r="C4" t="n">
-        <v>7255</v>
+        <v>6422</v>
       </c>
       <c r="D4" t="n">
-        <v>9834</v>
+        <v>8957</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1196</v>
+        <v>1161</v>
       </c>
       <c r="C5" t="n">
-        <v>3611</v>
+        <v>3547</v>
       </c>
       <c r="D5" t="n">
-        <v>2800</v>
+        <v>2662</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>664</v>
+        <v>700</v>
       </c>
       <c r="C6" t="n">
-        <v>2525</v>
+        <v>2615</v>
       </c>
       <c r="D6" t="n">
-        <v>774</v>
+        <v>788</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>304</v>
+        <v>335</v>
       </c>
       <c r="C7" t="n">
-        <v>1576</v>
+        <v>1688</v>
       </c>
       <c r="D7" t="n">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="C8" t="n">
-        <v>864</v>
+        <v>917</v>
       </c>
       <c r="D8" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12">
@@ -1856,7 +1856,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
         <v>123</v>
@@ -1867,7 +1867,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
         <v>87</v>
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4435</v>
+        <v>3604</v>
       </c>
       <c r="C2" t="n">
-        <v>4516</v>
+        <v>2943</v>
       </c>
       <c r="D2" t="n">
-        <v>13543</v>
+        <v>23456</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4967</v>
+        <v>4235</v>
       </c>
       <c r="C3" t="n">
-        <v>8154</v>
+        <v>7076</v>
       </c>
       <c r="D3" t="n">
-        <v>18500</v>
+        <v>20747</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2446</v>
+        <v>2245</v>
       </c>
       <c r="C4" t="n">
-        <v>8181</v>
+        <v>7647</v>
       </c>
       <c r="D4" t="n">
-        <v>11243</v>
+        <v>10543</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1321</v>
+        <v>1270</v>
       </c>
       <c r="C5" t="n">
-        <v>5213</v>
+        <v>4830</v>
       </c>
       <c r="D5" t="n">
-        <v>3646</v>
+        <v>3417</v>
       </c>
     </row>
     <row r="6">
@@ -2080,10 +2080,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>799</v>
+        <v>820</v>
       </c>
       <c r="C6" t="n">
-        <v>3029</v>
+        <v>3070</v>
       </c>
       <c r="D6" t="n">
         <v>981</v>
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>287</v>
+        <v>317</v>
       </c>
       <c r="C7" t="n">
-        <v>1974</v>
+        <v>2090</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="C8" t="n">
-        <v>1103</v>
+        <v>1173</v>
       </c>
       <c r="D8" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>470</v>
+        <v>487</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
+        <v>168</v>
+      </c>
+      <c r="D11" t="n">
         <v>166</v>
-      </c>
-      <c r="D11" t="n">
-        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2164,7 +2164,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
         <v>96</v>
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5043</v>
+        <v>3887</v>
       </c>
       <c r="C2" t="n">
-        <v>10467</v>
+        <v>4335</v>
       </c>
       <c r="D2" t="n">
-        <v>14508</v>
+        <v>19426</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3980</v>
+        <v>3332</v>
       </c>
       <c r="C3" t="n">
-        <v>5714</v>
+        <v>4552</v>
       </c>
       <c r="D3" t="n">
-        <v>16690</v>
+        <v>19908</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3048</v>
+        <v>2682</v>
       </c>
       <c r="C4" t="n">
-        <v>7997</v>
+        <v>7208</v>
       </c>
       <c r="D4" t="n">
-        <v>12085</v>
+        <v>11887</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1593</v>
+        <v>1496</v>
       </c>
       <c r="C5" t="n">
-        <v>6500</v>
+        <v>6054</v>
       </c>
       <c r="D5" t="n">
-        <v>4702</v>
+        <v>4407</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C6" t="n">
-        <v>4014</v>
+        <v>3864</v>
       </c>
       <c r="D6" t="n">
-        <v>1351</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="C7" t="n">
-        <v>2447</v>
+        <v>2511</v>
       </c>
       <c r="D7" t="n">
-        <v>577</v>
+        <v>583</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="C8" t="n">
-        <v>1463</v>
+        <v>1561</v>
       </c>
       <c r="D8" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>710</v>
+        <v>758</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2475,7 +2475,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
         <v>117</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2579,7 +2579,7 @@
         <v>58</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2966</v>
+        <v>2306</v>
       </c>
       <c r="C2" t="n">
-        <v>4880</v>
+        <v>2035</v>
       </c>
       <c r="D2" t="n">
-        <v>10155</v>
+        <v>13420</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4086</v>
+        <v>3343</v>
       </c>
       <c r="C3" t="n">
-        <v>7137</v>
+        <v>4331</v>
       </c>
       <c r="D3" t="n">
-        <v>16089</v>
+        <v>19376</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3366</v>
+        <v>2958</v>
       </c>
       <c r="C4" t="n">
-        <v>7853</v>
+        <v>6926</v>
       </c>
       <c r="D4" t="n">
-        <v>12740</v>
+        <v>13022</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1660</v>
+        <v>1587</v>
       </c>
       <c r="C5" t="n">
-        <v>7751</v>
+        <v>7174</v>
       </c>
       <c r="D5" t="n">
-        <v>4962</v>
+        <v>4672</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>777</v>
+        <v>800</v>
       </c>
       <c r="C6" t="n">
-        <v>4878</v>
+        <v>4733</v>
       </c>
       <c r="D6" t="n">
-        <v>1319</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="C7" t="n">
-        <v>2619</v>
+        <v>2713</v>
       </c>
       <c r="D7" t="n">
-        <v>577</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1140</v>
+        <v>1232</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2772,7 +2772,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
         <v>114</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2876,7 +2876,7 @@
         <v>56</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3165</v>
+        <v>2401</v>
       </c>
       <c r="C2" t="n">
-        <v>6312</v>
+        <v>7100</v>
       </c>
       <c r="D2" t="n">
-        <v>19015</v>
+        <v>13399</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3096</v>
+        <v>2465</v>
       </c>
       <c r="C3" t="n">
-        <v>5446</v>
+        <v>2909</v>
       </c>
       <c r="D3" t="n">
-        <v>14355</v>
+        <v>17263</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3193</v>
+        <v>2752</v>
       </c>
       <c r="C4" t="n">
-        <v>7352</v>
+        <v>5602</v>
       </c>
       <c r="D4" t="n">
-        <v>12867</v>
+        <v>13663</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2075</v>
+        <v>1904</v>
       </c>
       <c r="C5" t="n">
-        <v>7710</v>
+        <v>6981</v>
       </c>
       <c r="D5" t="n">
-        <v>5931</v>
+        <v>5857</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="C6" t="n">
-        <v>6094</v>
+        <v>5766</v>
       </c>
       <c r="D6" t="n">
-        <v>1791</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="C7" t="n">
         <v>3576</v>
       </c>
       <c r="D7" t="n">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>1698</v>
+        <v>1792</v>
       </c>
       <c r="D8" t="n">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>589</v>
+        <v>623</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3075,7 +3075,7 @@
         <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3083,7 +3083,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
         <v>135</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3173,7 +3173,7 @@
         <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2172</v>
+        <v>1645</v>
       </c>
       <c r="C2" t="n">
-        <v>4139</v>
+        <v>3519</v>
       </c>
       <c r="D2" t="n">
-        <v>13745</v>
+        <v>10986</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2732</v>
+        <v>2140</v>
       </c>
       <c r="C3" t="n">
-        <v>5254</v>
+        <v>4147</v>
       </c>
       <c r="D3" t="n">
-        <v>14133</v>
+        <v>15860</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2913</v>
+        <v>2456</v>
       </c>
       <c r="C4" t="n">
-        <v>6642</v>
+        <v>4535</v>
       </c>
       <c r="D4" t="n">
-        <v>12922</v>
+        <v>13862</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2266</v>
+        <v>2069</v>
       </c>
       <c r="C5" t="n">
-        <v>7644</v>
+        <v>6600</v>
       </c>
       <c r="D5" t="n">
-        <v>6540</v>
+        <v>6690</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1207</v>
+        <v>1173</v>
       </c>
       <c r="C6" t="n">
-        <v>6847</v>
+        <v>6382</v>
       </c>
       <c r="D6" t="n">
-        <v>2179</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>263</v>
+        <v>286</v>
       </c>
       <c r="C7" t="n">
-        <v>4436</v>
+        <v>4356</v>
       </c>
       <c r="D7" t="n">
-        <v>750</v>
+        <v>765</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>2187</v>
+        <v>2253</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>664</v>
+        <v>720</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
         <v>92</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3470,7 +3470,7 @@
         <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4143</v>
+        <v>3298</v>
       </c>
       <c r="C2" t="n">
-        <v>11339</v>
+        <v>17263</v>
       </c>
       <c r="D2" t="n">
-        <v>18597</v>
+        <v>17208</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2138</v>
+        <v>1653</v>
       </c>
       <c r="C3" t="n">
-        <v>4281</v>
+        <v>3456</v>
       </c>
       <c r="D3" t="n">
-        <v>13181</v>
+        <v>14260</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2477</v>
+        <v>2037</v>
       </c>
       <c r="C4" t="n">
-        <v>5917</v>
+        <v>4273</v>
       </c>
       <c r="D4" t="n">
-        <v>12703</v>
+        <v>13728</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2263</v>
+        <v>2011</v>
       </c>
       <c r="C5" t="n">
-        <v>7080</v>
+        <v>5610</v>
       </c>
       <c r="D5" t="n">
-        <v>7198</v>
+        <v>7386</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1452</v>
+        <v>1381</v>
       </c>
       <c r="C6" t="n">
-        <v>7095</v>
+        <v>6412</v>
       </c>
       <c r="D6" t="n">
-        <v>2695</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>494</v>
+        <v>509</v>
       </c>
       <c r="C7" t="n">
-        <v>5375</v>
+        <v>5171</v>
       </c>
       <c r="D7" t="n">
-        <v>910</v>
+        <v>927</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>2957</v>
+        <v>2994</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1162</v>
+        <v>1237</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
         <v>37</v>
@@ -3781,7 +3781,7 @@
         <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4580</v>
+        <v>5933</v>
       </c>
       <c r="C2" t="n">
-        <v>9258</v>
+        <v>9271</v>
       </c>
       <c r="D2" t="n">
-        <v>9780</v>
+        <v>14232</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2993</v>
+        <v>2358</v>
       </c>
       <c r="C2" t="n">
-        <v>6532</v>
+        <v>9806</v>
       </c>
       <c r="D2" t="n">
-        <v>13836</v>
+        <v>12665</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2954</v>
+        <v>2340</v>
       </c>
       <c r="C3" t="n">
-        <v>6238</v>
+        <v>6957</v>
       </c>
       <c r="D3" t="n">
-        <v>14548</v>
+        <v>15713</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3357</v>
+        <v>2895</v>
       </c>
       <c r="C4" t="n">
-        <v>8334</v>
+        <v>6190</v>
       </c>
       <c r="D4" t="n">
-        <v>13068</v>
+        <v>13958</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1383</v>
+        <v>1331</v>
       </c>
       <c r="C5" t="n">
-        <v>10185</v>
+        <v>8689</v>
       </c>
       <c r="D5" t="n">
-        <v>6503</v>
+        <v>6705</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="C6" t="n">
-        <v>6588</v>
+        <v>6324</v>
       </c>
       <c r="D6" t="n">
-        <v>2096</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C7" t="n">
-        <v>2897</v>
+        <v>2934</v>
       </c>
       <c r="D7" t="n">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>1138</v>
+        <v>1212</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
         <v>36</v>
@@ -4389,7 +4389,7 @@
         <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6201</v>
+        <v>6503</v>
       </c>
       <c r="C2" t="n">
-        <v>5308</v>
+        <v>6907</v>
       </c>
       <c r="D2" t="n">
-        <v>17247</v>
+        <v>19266</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1947</v>
+        <v>2521</v>
       </c>
       <c r="C3" t="n">
-        <v>4666</v>
+        <v>4672</v>
       </c>
       <c r="D3" t="n">
-        <v>2282</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4704</v>
+        <v>4909</v>
       </c>
       <c r="C2" t="n">
-        <v>4862</v>
+        <v>3855</v>
       </c>
       <c r="D2" t="n">
-        <v>17870</v>
+        <v>17833</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3342</v>
+        <v>3705</v>
       </c>
       <c r="C3" t="n">
-        <v>4337</v>
+        <v>5119</v>
       </c>
       <c r="D3" t="n">
-        <v>4628</v>
+        <v>5534</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>880</v>
+        <v>1129</v>
       </c>
       <c r="C4" t="n">
-        <v>2778</v>
+        <v>2781</v>
       </c>
       <c r="D4" t="n">
-        <v>1641</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -4896,7 +4896,7 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5200</v>
+        <v>4478</v>
       </c>
       <c r="C2" t="n">
-        <v>4403</v>
+        <v>5894</v>
       </c>
       <c r="D2" t="n">
-        <v>25383</v>
+        <v>16438</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3296</v>
+        <v>3534</v>
       </c>
       <c r="C3" t="n">
-        <v>4001</v>
+        <v>3834</v>
       </c>
       <c r="D3" t="n">
-        <v>6413</v>
+        <v>7103</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1792</v>
+        <v>2056</v>
       </c>
       <c r="C4" t="n">
-        <v>3603</v>
+        <v>4047</v>
       </c>
       <c r="D4" t="n">
-        <v>2164</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>414</v>
+        <v>514</v>
       </c>
       <c r="C5" t="n">
-        <v>1614</v>
+        <v>1618</v>
       </c>
       <c r="D5" t="n">
-        <v>1230</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
         <v>908</v>
@@ -5207,10 +5207,10 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="D7" t="n">
-        <v>620</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4853</v>
+        <v>4654</v>
       </c>
       <c r="C2" t="n">
-        <v>5748</v>
+        <v>5193</v>
       </c>
       <c r="D2" t="n">
-        <v>29719</v>
+        <v>17972</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3443</v>
+        <v>3309</v>
       </c>
       <c r="C3" t="n">
-        <v>3662</v>
+        <v>4259</v>
       </c>
       <c r="D3" t="n">
-        <v>8844</v>
+        <v>8021</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2159</v>
+        <v>2348</v>
       </c>
       <c r="C4" t="n">
-        <v>3742</v>
+        <v>3848</v>
       </c>
       <c r="D4" t="n">
-        <v>2873</v>
+        <v>3228</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>901</v>
+        <v>1054</v>
       </c>
       <c r="C5" t="n">
-        <v>2596</v>
+        <v>2828</v>
       </c>
       <c r="D5" t="n">
-        <v>1342</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>247</v>
+        <v>288</v>
       </c>
       <c r="C6" t="n">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="D6" t="n">
-        <v>951</v>
+        <v>955</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D7" t="n">
-        <v>655</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D8" t="n">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
         <v>187</v>
@@ -5588,7 +5588,7 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5583</v>
+        <v>5291</v>
       </c>
       <c r="C2" t="n">
-        <v>10274</v>
+        <v>8691</v>
       </c>
       <c r="D2" t="n">
-        <v>43166</v>
+        <v>31981</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3004</v>
+        <v>2884</v>
       </c>
       <c r="C3" t="n">
-        <v>3873</v>
+        <v>3880</v>
       </c>
       <c r="D3" t="n">
-        <v>10719</v>
+        <v>8438</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1726</v>
+        <v>1745</v>
       </c>
       <c r="C4" t="n">
-        <v>3028</v>
+        <v>3337</v>
       </c>
       <c r="D4" t="n">
-        <v>3381</v>
+        <v>3491</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>799</v>
+        <v>892</v>
       </c>
       <c r="C5" t="n">
-        <v>2309</v>
+        <v>2428</v>
       </c>
       <c r="D5" t="n">
-        <v>1257</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>269</v>
+        <v>315</v>
       </c>
       <c r="C6" t="n">
-        <v>1204</v>
+        <v>1284</v>
       </c>
       <c r="D6" t="n">
-        <v>774</v>
+        <v>786</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C7" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D7" t="n">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5577</v>
+        <v>4537</v>
       </c>
       <c r="C2" t="n">
-        <v>6411</v>
+        <v>6528</v>
       </c>
       <c r="D2" t="n">
-        <v>31831</v>
+        <v>33292</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3570</v>
+        <v>3398</v>
       </c>
       <c r="C3" t="n">
-        <v>6553</v>
+        <v>5758</v>
       </c>
       <c r="D3" t="n">
-        <v>15381</v>
+        <v>11772</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2077</v>
+        <v>2030</v>
       </c>
       <c r="C4" t="n">
-        <v>3476</v>
+        <v>3595</v>
       </c>
       <c r="D4" t="n">
-        <v>4725</v>
+        <v>4348</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1126</v>
+        <v>1170</v>
       </c>
       <c r="C5" t="n">
-        <v>2682</v>
+        <v>2886</v>
       </c>
       <c r="D5" t="n">
-        <v>1646</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>491</v>
+        <v>563</v>
       </c>
       <c r="C6" t="n">
-        <v>1803</v>
+        <v>1927</v>
       </c>
       <c r="D6" t="n">
-        <v>855</v>
+        <v>883</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="C7" t="n">
-        <v>862</v>
+        <v>908</v>
       </c>
       <c r="D7" t="n">
-        <v>549</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8">
@@ -6151,7 +6151,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
         <v>327</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
         <v>120</v>
@@ -6238,7 +6238,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4808</v>
+        <v>3799</v>
       </c>
       <c r="C2" t="n">
-        <v>4626</v>
+        <v>3683</v>
       </c>
       <c r="D2" t="n">
-        <v>32690</v>
+        <v>36197</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3737</v>
+        <v>3255</v>
       </c>
       <c r="C3" t="n">
-        <v>5605</v>
+        <v>5347</v>
       </c>
       <c r="D3" t="n">
-        <v>16905</v>
+        <v>14367</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2428</v>
+        <v>2317</v>
       </c>
       <c r="C4" t="n">
-        <v>5146</v>
+        <v>4745</v>
       </c>
       <c r="D4" t="n">
-        <v>6627</v>
+        <v>5641</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1393</v>
+        <v>1413</v>
       </c>
       <c r="C5" t="n">
-        <v>3060</v>
+        <v>3213</v>
       </c>
       <c r="D5" t="n">
-        <v>2141</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>732</v>
+        <v>783</v>
       </c>
       <c r="C6" t="n">
-        <v>2228</v>
+        <v>2392</v>
       </c>
       <c r="D6" t="n">
-        <v>987</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>284</v>
+        <v>332</v>
       </c>
       <c r="C7" t="n">
-        <v>1359</v>
+        <v>1446</v>
       </c>
       <c r="D7" t="n">
-        <v>591</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C8" t="n">
-        <v>599</v>
+        <v>622</v>
       </c>
       <c r="D8" t="n">
         <v>410</v>
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
         <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6510,7 +6510,7 @@
         <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -6633,7 +6633,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_84_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_84_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5670</v>
+        <v>897</v>
       </c>
       <c r="C2" t="n">
-        <v>6361</v>
+        <v>4570</v>
       </c>
       <c r="D2" t="n">
-        <v>32534</v>
+        <v>20374</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2892</v>
+        <v>1660</v>
       </c>
       <c r="C3" t="n">
-        <v>3930</v>
+        <v>9632</v>
       </c>
       <c r="D3" t="n">
-        <v>16811</v>
+        <v>13292</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2353</v>
+        <v>1159</v>
       </c>
       <c r="C4" t="n">
-        <v>4964</v>
+        <v>11969</v>
       </c>
       <c r="D4" t="n">
-        <v>6923</v>
+        <v>5057</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1612</v>
+        <v>557</v>
       </c>
       <c r="C5" t="n">
-        <v>3925</v>
+        <v>6681</v>
       </c>
       <c r="D5" t="n">
-        <v>2685</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>988</v>
+        <v>234</v>
       </c>
       <c r="C6" t="n">
-        <v>2745</v>
+        <v>2319</v>
       </c>
       <c r="D6" t="n">
-        <v>1185</v>
+        <v>730</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>480</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>1908</v>
+        <v>805</v>
       </c>
       <c r="D7" t="n">
-        <v>665</v>
+        <v>486</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>1009</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>424</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>242</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6113</v>
+        <v>1224</v>
       </c>
       <c r="C2" t="n">
-        <v>10466</v>
+        <v>14697</v>
       </c>
       <c r="D2" t="n">
-        <v>32871</v>
+        <v>27376</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3334</v>
+        <v>1107</v>
       </c>
       <c r="C3" t="n">
-        <v>4430</v>
+        <v>6171</v>
       </c>
       <c r="D3" t="n">
-        <v>17819</v>
+        <v>13560</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2237</v>
+        <v>1209</v>
       </c>
       <c r="C4" t="n">
-        <v>4316</v>
+        <v>10601</v>
       </c>
       <c r="D4" t="n">
-        <v>8259</v>
+        <v>6326</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1710</v>
+        <v>733</v>
       </c>
       <c r="C5" t="n">
-        <v>4332</v>
+        <v>9181</v>
       </c>
       <c r="D5" t="n">
-        <v>3295</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1146</v>
+        <v>336</v>
       </c>
       <c r="C6" t="n">
-        <v>3223</v>
+        <v>4411</v>
       </c>
       <c r="D6" t="n">
-        <v>1399</v>
+        <v>869</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>626</v>
+        <v>137</v>
       </c>
       <c r="C7" t="n">
-        <v>2284</v>
+        <v>1509</v>
       </c>
       <c r="D7" t="n">
-        <v>728</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>275</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>1386</v>
+        <v>551</v>
       </c>
       <c r="D8" t="n">
-        <v>461</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>670</v>
+        <v>313</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>301</v>
+        <v>240</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6225</v>
+        <v>669</v>
       </c>
       <c r="C2" t="n">
-        <v>9810</v>
+        <v>6417</v>
       </c>
       <c r="D2" t="n">
-        <v>42018</v>
+        <v>18634</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3619</v>
+        <v>1105</v>
       </c>
       <c r="C3" t="n">
-        <v>6148</v>
+        <v>9081</v>
       </c>
       <c r="D3" t="n">
-        <v>18576</v>
+        <v>14870</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2280</v>
+        <v>1302</v>
       </c>
       <c r="C4" t="n">
-        <v>4235</v>
+        <v>9883</v>
       </c>
       <c r="D4" t="n">
-        <v>9476</v>
+        <v>7261</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1716</v>
+        <v>723</v>
       </c>
       <c r="C5" t="n">
-        <v>4234</v>
+        <v>10782</v>
       </c>
       <c r="D5" t="n">
-        <v>3878</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1257</v>
+        <v>269</v>
       </c>
       <c r="C6" t="n">
-        <v>3620</v>
+        <v>5341</v>
       </c>
       <c r="D6" t="n">
-        <v>1653</v>
+        <v>887</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>758</v>
+        <v>71</v>
       </c>
       <c r="C7" t="n">
-        <v>2669</v>
+        <v>1391</v>
       </c>
       <c r="D7" t="n">
-        <v>805</v>
+        <v>544</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>363</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1723</v>
+        <v>490</v>
       </c>
       <c r="D8" t="n">
-        <v>492</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>146</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>936</v>
+        <v>235</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>438</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>225</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5758</v>
+        <v>757</v>
       </c>
       <c r="C2" t="n">
-        <v>6670</v>
+        <v>7115</v>
       </c>
       <c r="D2" t="n">
-        <v>34327</v>
+        <v>15756</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4255</v>
+        <v>785</v>
       </c>
       <c r="C3" t="n">
-        <v>8786</v>
+        <v>6941</v>
       </c>
       <c r="D3" t="n">
-        <v>19939</v>
+        <v>14531</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1585</v>
+        <v>1084</v>
       </c>
       <c r="C4" t="n">
-        <v>6422</v>
+        <v>9284</v>
       </c>
       <c r="D4" t="n">
-        <v>8957</v>
+        <v>8282</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1161</v>
+        <v>858</v>
       </c>
       <c r="C5" t="n">
-        <v>3547</v>
+        <v>10238</v>
       </c>
       <c r="D5" t="n">
-        <v>2662</v>
+        <v>3105</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>700</v>
+        <v>399</v>
       </c>
       <c r="C6" t="n">
-        <v>2615</v>
+        <v>7797</v>
       </c>
       <c r="D6" t="n">
-        <v>788</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>335</v>
+        <v>120</v>
       </c>
       <c r="C7" t="n">
-        <v>1688</v>
+        <v>3043</v>
       </c>
       <c r="D7" t="n">
-        <v>482</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>134</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>917</v>
+        <v>834</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>429</v>
+        <v>326</v>
       </c>
       <c r="D9" t="n">
-        <v>248</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3604</v>
+        <v>387</v>
       </c>
       <c r="C2" t="n">
-        <v>2943</v>
+        <v>5192</v>
       </c>
       <c r="D2" t="n">
-        <v>23456</v>
+        <v>12379</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4235</v>
+        <v>678</v>
       </c>
       <c r="C3" t="n">
-        <v>7076</v>
+        <v>6406</v>
       </c>
       <c r="D3" t="n">
-        <v>20747</v>
+        <v>14013</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2245</v>
+        <v>915</v>
       </c>
       <c r="C4" t="n">
-        <v>7647</v>
+        <v>8368</v>
       </c>
       <c r="D4" t="n">
-        <v>10543</v>
+        <v>8949</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1270</v>
+        <v>903</v>
       </c>
       <c r="C5" t="n">
-        <v>4830</v>
+        <v>10061</v>
       </c>
       <c r="D5" t="n">
-        <v>3417</v>
+        <v>3666</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>820</v>
+        <v>480</v>
       </c>
       <c r="C6" t="n">
-        <v>3070</v>
+        <v>8897</v>
       </c>
       <c r="D6" t="n">
-        <v>981</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>317</v>
+        <v>123</v>
       </c>
       <c r="C7" t="n">
-        <v>2090</v>
+        <v>4461</v>
       </c>
       <c r="D7" t="n">
-        <v>526</v>
+        <v>632</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>1173</v>
+        <v>1288</v>
       </c>
       <c r="D8" t="n">
-        <v>337</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>487</v>
+        <v>398</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3887</v>
+        <v>303</v>
       </c>
       <c r="C2" t="n">
-        <v>4335</v>
+        <v>5980</v>
       </c>
       <c r="D2" t="n">
-        <v>19426</v>
+        <v>20996</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3332</v>
+        <v>481</v>
       </c>
       <c r="C3" t="n">
-        <v>4552</v>
+        <v>5231</v>
       </c>
       <c r="D3" t="n">
-        <v>19908</v>
+        <v>13019</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2682</v>
+        <v>720</v>
       </c>
       <c r="C4" t="n">
-        <v>7208</v>
+        <v>7407</v>
       </c>
       <c r="D4" t="n">
-        <v>11887</v>
+        <v>9320</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1496</v>
+        <v>840</v>
       </c>
       <c r="C5" t="n">
-        <v>6054</v>
+        <v>9152</v>
       </c>
       <c r="D5" t="n">
-        <v>4407</v>
+        <v>4315</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>930</v>
+        <v>581</v>
       </c>
       <c r="C6" t="n">
-        <v>3864</v>
+        <v>9278</v>
       </c>
       <c r="D6" t="n">
-        <v>1318</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>457</v>
+        <v>212</v>
       </c>
       <c r="C7" t="n">
-        <v>2511</v>
+        <v>6154</v>
       </c>
       <c r="D7" t="n">
-        <v>583</v>
+        <v>709</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>162</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>1561</v>
+        <v>2450</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>758</v>
+        <v>698</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>326</v>
+        <v>277</v>
       </c>
       <c r="D10" t="n">
-        <v>214</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2306</v>
+        <v>213</v>
       </c>
       <c r="C2" t="n">
-        <v>2035</v>
+        <v>3396</v>
       </c>
       <c r="D2" t="n">
-        <v>13420</v>
+        <v>15454</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3343</v>
+        <v>665</v>
       </c>
       <c r="C3" t="n">
-        <v>4331</v>
+        <v>5856</v>
       </c>
       <c r="D3" t="n">
-        <v>19376</v>
+        <v>14468</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2958</v>
+        <v>1139</v>
       </c>
       <c r="C4" t="n">
-        <v>6926</v>
+        <v>10474</v>
       </c>
       <c r="D4" t="n">
-        <v>13022</v>
+        <v>9315</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1587</v>
+        <v>560</v>
       </c>
       <c r="C5" t="n">
-        <v>7174</v>
+        <v>13248</v>
       </c>
       <c r="D5" t="n">
-        <v>4672</v>
+        <v>3927</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>800</v>
+        <v>195</v>
       </c>
       <c r="C6" t="n">
-        <v>4733</v>
+        <v>7849</v>
       </c>
       <c r="D6" t="n">
-        <v>1292</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>149</v>
+        <v>59</v>
       </c>
       <c r="C7" t="n">
-        <v>2713</v>
+        <v>2401</v>
       </c>
       <c r="D7" t="n">
-        <v>582</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>1232</v>
+        <v>684</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>319</v>
+        <v>271</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2401</v>
+        <v>132</v>
       </c>
       <c r="C2" t="n">
-        <v>7100</v>
+        <v>1852</v>
       </c>
       <c r="D2" t="n">
-        <v>13399</v>
+        <v>10767</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2465</v>
+        <v>419</v>
       </c>
       <c r="C3" t="n">
-        <v>2909</v>
+        <v>4205</v>
       </c>
       <c r="D3" t="n">
-        <v>17263</v>
+        <v>13585</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2752</v>
+        <v>779</v>
       </c>
       <c r="C4" t="n">
-        <v>5602</v>
+        <v>7841</v>
       </c>
       <c r="D4" t="n">
-        <v>13663</v>
+        <v>9445</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1904</v>
+        <v>542</v>
       </c>
       <c r="C5" t="n">
-        <v>6981</v>
+        <v>10550</v>
       </c>
       <c r="D5" t="n">
-        <v>5857</v>
+        <v>4191</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1008</v>
+        <v>189</v>
       </c>
       <c r="C6" t="n">
-        <v>5766</v>
+        <v>8214</v>
       </c>
       <c r="D6" t="n">
-        <v>1729</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>306</v>
+        <v>45</v>
       </c>
       <c r="C7" t="n">
-        <v>3576</v>
+        <v>3202</v>
       </c>
       <c r="D7" t="n">
-        <v>672</v>
+        <v>530</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>1792</v>
+        <v>806</v>
       </c>
       <c r="D8" t="n">
-        <v>393</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>623</v>
+        <v>250</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>115</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1645</v>
+        <v>201</v>
       </c>
       <c r="C2" t="n">
-        <v>3519</v>
+        <v>7661</v>
       </c>
       <c r="D2" t="n">
-        <v>10986</v>
+        <v>9346</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2140</v>
+        <v>247</v>
       </c>
       <c r="C3" t="n">
-        <v>4147</v>
+        <v>2656</v>
       </c>
       <c r="D3" t="n">
-        <v>15860</v>
+        <v>12244</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2456</v>
+        <v>542</v>
       </c>
       <c r="C4" t="n">
-        <v>4535</v>
+        <v>5793</v>
       </c>
       <c r="D4" t="n">
-        <v>13862</v>
+        <v>9873</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2069</v>
+        <v>584</v>
       </c>
       <c r="C5" t="n">
-        <v>6600</v>
+        <v>9079</v>
       </c>
       <c r="D5" t="n">
-        <v>6690</v>
+        <v>4921</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1173</v>
+        <v>307</v>
       </c>
       <c r="C6" t="n">
-        <v>6382</v>
+        <v>9229</v>
       </c>
       <c r="D6" t="n">
-        <v>2098</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>286</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>4356</v>
+        <v>5540</v>
       </c>
       <c r="D7" t="n">
-        <v>765</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>2253</v>
+        <v>1846</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>720</v>
+        <v>475</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>166</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3298</v>
+        <v>334</v>
       </c>
       <c r="C2" t="n">
-        <v>17263</v>
+        <v>16168</v>
       </c>
       <c r="D2" t="n">
-        <v>17208</v>
+        <v>10779</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1653</v>
+        <v>192</v>
       </c>
       <c r="C3" t="n">
-        <v>3456</v>
+        <v>4303</v>
       </c>
       <c r="D3" t="n">
-        <v>14260</v>
+        <v>11027</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2037</v>
+        <v>365</v>
       </c>
       <c r="C4" t="n">
-        <v>4273</v>
+        <v>4196</v>
       </c>
       <c r="D4" t="n">
-        <v>13728</v>
+        <v>9959</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2011</v>
+        <v>520</v>
       </c>
       <c r="C5" t="n">
-        <v>5610</v>
+        <v>7407</v>
       </c>
       <c r="D5" t="n">
-        <v>7386</v>
+        <v>5532</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1381</v>
+        <v>384</v>
       </c>
       <c r="C6" t="n">
-        <v>6412</v>
+        <v>8987</v>
       </c>
       <c r="D6" t="n">
-        <v>2687</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>509</v>
+        <v>154</v>
       </c>
       <c r="C7" t="n">
-        <v>5171</v>
+        <v>7128</v>
       </c>
       <c r="D7" t="n">
-        <v>927</v>
+        <v>825</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>41</v>
       </c>
       <c r="C8" t="n">
-        <v>2994</v>
+        <v>3365</v>
       </c>
       <c r="D8" t="n">
-        <v>444</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>1237</v>
+        <v>1012</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>383</v>
+        <v>281</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5933</v>
+        <v>3300</v>
       </c>
       <c r="C2" t="n">
-        <v>9271</v>
+        <v>12673</v>
       </c>
       <c r="D2" t="n">
-        <v>14232</v>
+        <v>7865</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2358</v>
+        <v>315</v>
       </c>
       <c r="C2" t="n">
-        <v>9806</v>
+        <v>13507</v>
       </c>
       <c r="D2" t="n">
-        <v>12665</v>
+        <v>20840</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2340</v>
+        <v>200</v>
       </c>
       <c r="C3" t="n">
-        <v>6957</v>
+        <v>7916</v>
       </c>
       <c r="D3" t="n">
-        <v>15713</v>
+        <v>10291</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2895</v>
+        <v>261</v>
       </c>
       <c r="C4" t="n">
-        <v>6190</v>
+        <v>4112</v>
       </c>
       <c r="D4" t="n">
-        <v>13958</v>
+        <v>9810</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1331</v>
+        <v>430</v>
       </c>
       <c r="C5" t="n">
-        <v>8689</v>
+        <v>5958</v>
       </c>
       <c r="D5" t="n">
-        <v>6705</v>
+        <v>5905</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>470</v>
+        <v>399</v>
       </c>
       <c r="C6" t="n">
-        <v>6324</v>
+        <v>8216</v>
       </c>
       <c r="D6" t="n">
-        <v>2106</v>
+        <v>2656</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>101</v>
+        <v>211</v>
       </c>
       <c r="C7" t="n">
-        <v>2934</v>
+        <v>7765</v>
       </c>
       <c r="D7" t="n">
-        <v>553</v>
+        <v>989</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>1212</v>
+        <v>4764</v>
       </c>
       <c r="D8" t="n">
-        <v>299</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>375</v>
+        <v>1831</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>158</v>
+        <v>531</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>92</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>59</v>
+      </c>
+      <c r="D13" t="n">
         <v>38</v>
-      </c>
-      <c r="D13" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6503</v>
+        <v>3974</v>
       </c>
       <c r="C2" t="n">
-        <v>6907</v>
+        <v>11046</v>
       </c>
       <c r="D2" t="n">
-        <v>19266</v>
+        <v>14691</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2521</v>
+        <v>1092</v>
       </c>
       <c r="C3" t="n">
-        <v>4672</v>
+        <v>5004</v>
       </c>
       <c r="D3" t="n">
-        <v>3030</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4909</v>
+        <v>2506</v>
       </c>
       <c r="C2" t="n">
-        <v>3855</v>
+        <v>7275</v>
       </c>
       <c r="D2" t="n">
-        <v>17833</v>
+        <v>14955</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3705</v>
+        <v>2144</v>
       </c>
       <c r="C3" t="n">
-        <v>5119</v>
+        <v>7425</v>
       </c>
       <c r="D3" t="n">
-        <v>5534</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1129</v>
+        <v>531</v>
       </c>
       <c r="C4" t="n">
-        <v>2781</v>
+        <v>3170</v>
       </c>
       <c r="D4" t="n">
-        <v>1792</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>327</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4478</v>
+        <v>2211</v>
       </c>
       <c r="C2" t="n">
-        <v>5894</v>
+        <v>12278</v>
       </c>
       <c r="D2" t="n">
-        <v>16438</v>
+        <v>19042</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3534</v>
+        <v>1919</v>
       </c>
       <c r="C3" t="n">
-        <v>3834</v>
+        <v>6317</v>
       </c>
       <c r="D3" t="n">
-        <v>7103</v>
+        <v>5435</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2056</v>
+        <v>1176</v>
       </c>
       <c r="C4" t="n">
-        <v>4047</v>
+        <v>5636</v>
       </c>
       <c r="D4" t="n">
-        <v>2455</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>514</v>
+        <v>274</v>
       </c>
       <c r="C5" t="n">
-        <v>1618</v>
+        <v>1908</v>
       </c>
       <c r="D5" t="n">
-        <v>1258</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>261</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>401</v>
+        <v>334</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4654</v>
+        <v>2498</v>
       </c>
       <c r="C2" t="n">
-        <v>5193</v>
+        <v>14360</v>
       </c>
       <c r="D2" t="n">
-        <v>17972</v>
+        <v>21794</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3309</v>
+        <v>1700</v>
       </c>
       <c r="C3" t="n">
-        <v>4259</v>
+        <v>8281</v>
       </c>
       <c r="D3" t="n">
-        <v>8021</v>
+        <v>7220</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2348</v>
+        <v>1332</v>
       </c>
       <c r="C4" t="n">
-        <v>3848</v>
+        <v>5904</v>
       </c>
       <c r="D4" t="n">
-        <v>3228</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1054</v>
+        <v>607</v>
       </c>
       <c r="C5" t="n">
-        <v>2828</v>
+        <v>3908</v>
       </c>
       <c r="D5" t="n">
-        <v>1414</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>288</v>
+        <v>173</v>
       </c>
       <c r="C6" t="n">
-        <v>969</v>
+        <v>1127</v>
       </c>
       <c r="D6" t="n">
-        <v>955</v>
+        <v>835</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>374</v>
+        <v>310</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>247</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5291</v>
+        <v>1753</v>
       </c>
       <c r="C2" t="n">
-        <v>8691</v>
+        <v>8975</v>
       </c>
       <c r="D2" t="n">
-        <v>31981</v>
+        <v>24994</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2884</v>
+        <v>1701</v>
       </c>
       <c r="C3" t="n">
-        <v>3880</v>
+        <v>9895</v>
       </c>
       <c r="D3" t="n">
-        <v>8438</v>
+        <v>8926</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1745</v>
+        <v>1290</v>
       </c>
       <c r="C4" t="n">
-        <v>3337</v>
+        <v>6979</v>
       </c>
       <c r="D4" t="n">
-        <v>3491</v>
+        <v>3296</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>892</v>
+        <v>830</v>
       </c>
       <c r="C5" t="n">
-        <v>2428</v>
+        <v>4861</v>
       </c>
       <c r="D5" t="n">
-        <v>1353</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="C6" t="n">
-        <v>1284</v>
+        <v>2503</v>
       </c>
       <c r="D6" t="n">
-        <v>786</v>
+        <v>884</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="C7" t="n">
-        <v>415</v>
+        <v>702</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>620</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>302</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>272</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4537</v>
+        <v>1730</v>
       </c>
       <c r="C2" t="n">
-        <v>6528</v>
+        <v>12975</v>
       </c>
       <c r="D2" t="n">
-        <v>33292</v>
+        <v>35926</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3398</v>
+        <v>1429</v>
       </c>
       <c r="C3" t="n">
-        <v>5758</v>
+        <v>8316</v>
       </c>
       <c r="D3" t="n">
-        <v>11772</v>
+        <v>10511</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2030</v>
+        <v>1271</v>
       </c>
       <c r="C4" t="n">
-        <v>3595</v>
+        <v>8194</v>
       </c>
       <c r="D4" t="n">
-        <v>4348</v>
+        <v>4082</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1170</v>
+        <v>910</v>
       </c>
       <c r="C5" t="n">
-        <v>2886</v>
+        <v>5776</v>
       </c>
       <c r="D5" t="n">
-        <v>1742</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>563</v>
+        <v>498</v>
       </c>
       <c r="C6" t="n">
-        <v>1927</v>
+        <v>3564</v>
       </c>
       <c r="D6" t="n">
-        <v>883</v>
+        <v>937</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C7" t="n">
-        <v>908</v>
+        <v>1506</v>
       </c>
       <c r="D7" t="n">
-        <v>554</v>
+        <v>655</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="C8" t="n">
-        <v>327</v>
+        <v>478</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>144</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3799</v>
+        <v>1639</v>
       </c>
       <c r="C2" t="n">
-        <v>3683</v>
+        <v>8200</v>
       </c>
       <c r="D2" t="n">
-        <v>36197</v>
+        <v>28468</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3255</v>
+        <v>2044</v>
       </c>
       <c r="C3" t="n">
-        <v>5347</v>
+        <v>13073</v>
       </c>
       <c r="D3" t="n">
-        <v>14367</v>
+        <v>11538</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2317</v>
+        <v>840</v>
       </c>
       <c r="C4" t="n">
-        <v>4745</v>
+        <v>10500</v>
       </c>
       <c r="D4" t="n">
-        <v>5641</v>
+        <v>3845</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1413</v>
+        <v>460</v>
       </c>
       <c r="C5" t="n">
-        <v>3213</v>
+        <v>3492</v>
       </c>
       <c r="D5" t="n">
-        <v>2147</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>783</v>
+        <v>174</v>
       </c>
       <c r="C6" t="n">
-        <v>2392</v>
+        <v>1475</v>
       </c>
       <c r="D6" t="n">
-        <v>1027</v>
+        <v>641</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>332</v>
+        <v>89</v>
       </c>
       <c r="C7" t="n">
-        <v>1446</v>
+        <v>468</v>
       </c>
       <c r="D7" t="n">
-        <v>600</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>622</v>
+        <v>278</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>144</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
